--- a/output/yearly_population_iteration_57_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_57_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5475</v>
+        <v>7056</v>
       </c>
       <c r="C2" t="n">
-        <v>11025</v>
+        <v>5773</v>
       </c>
       <c r="D2" t="n">
-        <v>25281</v>
+        <v>23335</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3819</v>
+        <v>5049</v>
       </c>
       <c r="C3" t="n">
-        <v>7342</v>
+        <v>3578</v>
       </c>
       <c r="D3" t="n">
-        <v>17502</v>
+        <v>16253</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3025</v>
+        <v>3823</v>
       </c>
       <c r="C4" t="n">
-        <v>6689</v>
+        <v>3274</v>
       </c>
       <c r="D4" t="n">
-        <v>9930</v>
+        <v>8286</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1846</v>
+        <v>2400</v>
       </c>
       <c r="C5" t="n">
-        <v>5195</v>
+        <v>4030</v>
       </c>
       <c r="D5" t="n">
-        <v>3816</v>
+        <v>2899</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>968</v>
+        <v>1358</v>
       </c>
       <c r="C6" t="n">
-        <v>3365</v>
+        <v>3439</v>
       </c>
       <c r="D6" t="n">
-        <v>1411</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>434</v>
+        <v>648</v>
       </c>
       <c r="C7" t="n">
-        <v>1697</v>
+        <v>1999</v>
       </c>
       <c r="D7" t="n">
-        <v>686</v>
+        <v>649</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>156</v>
+        <v>241</v>
       </c>
       <c r="C8" t="n">
-        <v>710</v>
+        <v>893</v>
       </c>
       <c r="D8" t="n">
-        <v>435</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
-        <v>324</v>
+        <v>371</v>
       </c>
       <c r="D9" t="n">
         <v>304</v>
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
         <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
         <v>124</v>
@@ -951,7 +951,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7324</v>
+        <v>9098</v>
       </c>
       <c r="C2" t="n">
-        <v>9450</v>
+        <v>9311</v>
       </c>
       <c r="D2" t="n">
-        <v>37183</v>
+        <v>27930</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3704</v>
+        <v>4852</v>
       </c>
       <c r="C3" t="n">
-        <v>7898</v>
+        <v>4014</v>
       </c>
       <c r="D3" t="n">
-        <v>17349</v>
+        <v>16123</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2873</v>
+        <v>3750</v>
       </c>
       <c r="C4" t="n">
-        <v>6850</v>
+        <v>3348</v>
       </c>
       <c r="D4" t="n">
-        <v>10695</v>
+        <v>9334</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2079</v>
+        <v>2645</v>
       </c>
       <c r="C5" t="n">
-        <v>5696</v>
+        <v>3566</v>
       </c>
       <c r="D5" t="n">
-        <v>4639</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1203</v>
+        <v>1633</v>
       </c>
       <c r="C6" t="n">
-        <v>4090</v>
+        <v>3666</v>
       </c>
       <c r="D6" t="n">
-        <v>1724</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>582</v>
+        <v>853</v>
       </c>
       <c r="C7" t="n">
-        <v>2415</v>
+        <v>2599</v>
       </c>
       <c r="D7" t="n">
-        <v>785</v>
+        <v>710</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>235</v>
+        <v>356</v>
       </c>
       <c r="C8" t="n">
-        <v>1109</v>
+        <v>1358</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>453</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="C9" t="n">
-        <v>478</v>
+        <v>576</v>
       </c>
       <c r="D9" t="n">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>250</v>
+        <v>274</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1223,7 +1223,7 @@
         <v>180</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1276,7 +1276,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -1293,7 +1293,7 @@
         <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9341</v>
+        <v>9484</v>
       </c>
       <c r="C2" t="n">
-        <v>5898</v>
+        <v>7638</v>
       </c>
       <c r="D2" t="n">
-        <v>47668</v>
+        <v>24340</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4129</v>
+        <v>5297</v>
       </c>
       <c r="C3" t="n">
-        <v>7572</v>
+        <v>5509</v>
       </c>
       <c r="D3" t="n">
-        <v>18618</v>
+        <v>16507</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2727</v>
+        <v>3574</v>
       </c>
       <c r="C4" t="n">
-        <v>7074</v>
+        <v>3527</v>
       </c>
       <c r="D4" t="n">
-        <v>11328</v>
+        <v>9938</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2124</v>
+        <v>2738</v>
       </c>
       <c r="C5" t="n">
-        <v>5988</v>
+        <v>3367</v>
       </c>
       <c r="D5" t="n">
-        <v>5267</v>
+        <v>4324</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1409</v>
+        <v>1851</v>
       </c>
       <c r="C6" t="n">
-        <v>4686</v>
+        <v>3593</v>
       </c>
       <c r="D6" t="n">
-        <v>2093</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>726</v>
+        <v>1048</v>
       </c>
       <c r="C7" t="n">
-        <v>3030</v>
+        <v>2990</v>
       </c>
       <c r="D7" t="n">
-        <v>888</v>
+        <v>798</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>318</v>
+        <v>479</v>
       </c>
       <c r="C8" t="n">
-        <v>1584</v>
+        <v>1818</v>
       </c>
       <c r="D8" t="n">
-        <v>496</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9">
@@ -1500,10 +1500,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="C9" t="n">
-        <v>706</v>
+        <v>866</v>
       </c>
       <c r="D9" t="n">
         <v>328</v>
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>325</v>
+        <v>377</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1573,7 +1573,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -1587,7 +1587,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8465</v>
+        <v>8773</v>
       </c>
       <c r="C2" t="n">
-        <v>4152</v>
+        <v>5254</v>
       </c>
       <c r="D2" t="n">
-        <v>39028</v>
+        <v>20264</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4856</v>
+        <v>6384</v>
       </c>
       <c r="C3" t="n">
-        <v>10891</v>
+        <v>7600</v>
       </c>
       <c r="D3" t="n">
-        <v>20459</v>
+        <v>18107</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1962</v>
+        <v>2529</v>
       </c>
       <c r="C4" t="n">
-        <v>9483</v>
+        <v>5162</v>
       </c>
       <c r="D4" t="n">
-        <v>11086</v>
+        <v>9476</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1301</v>
+        <v>1710</v>
       </c>
       <c r="C5" t="n">
-        <v>4592</v>
+        <v>3521</v>
       </c>
       <c r="D5" t="n">
-        <v>3416</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>670</v>
+        <v>968</v>
       </c>
       <c r="C6" t="n">
-        <v>2969</v>
+        <v>2930</v>
       </c>
       <c r="D6" t="n">
-        <v>870</v>
+        <v>782</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>293</v>
+        <v>442</v>
       </c>
       <c r="C7" t="n">
-        <v>1552</v>
+        <v>1781</v>
       </c>
       <c r="D7" t="n">
-        <v>486</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -1797,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>112</v>
+        <v>168</v>
       </c>
       <c r="C8" t="n">
-        <v>691</v>
+        <v>848</v>
       </c>
       <c r="D8" t="n">
         <v>321</v>
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>318</v>
+        <v>369</v>
       </c>
       <c r="D9" t="n">
         <v>245</v>
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="D10" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
         <v>97</v>
@@ -1884,7 +1884,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
         <v>80</v>
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>38</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4952</v>
+        <v>5452</v>
       </c>
       <c r="C2" t="n">
-        <v>2953</v>
+        <v>2573</v>
       </c>
       <c r="D2" t="n">
-        <v>27701</v>
+        <v>13731</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5413</v>
+        <v>6397</v>
       </c>
       <c r="C3" t="n">
-        <v>7202</v>
+        <v>5937</v>
       </c>
       <c r="D3" t="n">
-        <v>21690</v>
+        <v>17531</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2635</v>
+        <v>3465</v>
       </c>
       <c r="C4" t="n">
-        <v>10285</v>
+        <v>6376</v>
       </c>
       <c r="D4" t="n">
-        <v>12311</v>
+        <v>10521</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1459</v>
+        <v>1913</v>
       </c>
       <c r="C5" t="n">
-        <v>6642</v>
+        <v>4244</v>
       </c>
       <c r="D5" t="n">
-        <v>4261</v>
+        <v>3602</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>798</v>
+        <v>1148</v>
       </c>
       <c r="C6" t="n">
-        <v>3651</v>
+        <v>3312</v>
       </c>
       <c r="D6" t="n">
-        <v>1105</v>
+        <v>989</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>271</v>
+        <v>412</v>
       </c>
       <c r="C7" t="n">
-        <v>2049</v>
+        <v>2223</v>
       </c>
       <c r="D7" t="n">
-        <v>531</v>
+        <v>510</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="C8" t="n">
-        <v>919</v>
+        <v>1131</v>
       </c>
       <c r="D8" t="n">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>354</v>
+        <v>413</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2167,7 +2167,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
         <v>130</v>
@@ -2181,7 +2181,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
         <v>99</v>
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4659</v>
+        <v>6035</v>
       </c>
       <c r="C2" t="n">
-        <v>7855</v>
+        <v>6369</v>
       </c>
       <c r="D2" t="n">
-        <v>25628</v>
+        <v>14955</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4391</v>
+        <v>5036</v>
       </c>
       <c r="C3" t="n">
-        <v>4707</v>
+        <v>3863</v>
       </c>
       <c r="D3" t="n">
-        <v>21049</v>
+        <v>15945</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3259</v>
+        <v>4089</v>
       </c>
       <c r="C4" t="n">
-        <v>8620</v>
+        <v>6028</v>
       </c>
       <c r="D4" t="n">
-        <v>13467</v>
+        <v>11345</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1720</v>
+        <v>2282</v>
       </c>
       <c r="C5" t="n">
-        <v>8147</v>
+        <v>5158</v>
       </c>
       <c r="D5" t="n">
-        <v>5367</v>
+        <v>4555</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>967</v>
+        <v>1347</v>
       </c>
       <c r="C6" t="n">
-        <v>4944</v>
+        <v>3732</v>
       </c>
       <c r="D6" t="n">
-        <v>1544</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>411</v>
+        <v>620</v>
       </c>
       <c r="C7" t="n">
-        <v>2727</v>
+        <v>2713</v>
       </c>
       <c r="D7" t="n">
-        <v>604</v>
+        <v>570</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>135</v>
+        <v>205</v>
       </c>
       <c r="C8" t="n">
-        <v>1350</v>
+        <v>1580</v>
       </c>
       <c r="D8" t="n">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>565</v>
+        <v>684</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
         <v>132</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2827</v>
+        <v>3618</v>
       </c>
       <c r="C2" t="n">
-        <v>3804</v>
+        <v>3000</v>
       </c>
       <c r="D2" t="n">
-        <v>17871</v>
+        <v>10325</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4298</v>
+        <v>5090</v>
       </c>
       <c r="C3" t="n">
-        <v>5586</v>
+        <v>4550</v>
       </c>
       <c r="D3" t="n">
-        <v>21053</v>
+        <v>15604</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3575</v>
+        <v>4506</v>
       </c>
       <c r="C4" t="n">
-        <v>8066</v>
+        <v>5811</v>
       </c>
       <c r="D4" t="n">
-        <v>14462</v>
+        <v>11985</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1757</v>
+        <v>2383</v>
       </c>
       <c r="C5" t="n">
-        <v>9629</v>
+        <v>6110</v>
       </c>
       <c r="D5" t="n">
-        <v>5618</v>
+        <v>4801</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>755</v>
+        <v>1120</v>
       </c>
       <c r="C6" t="n">
-        <v>5600</v>
+        <v>4622</v>
       </c>
       <c r="D6" t="n">
-        <v>1479</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>124</v>
+        <v>189</v>
       </c>
       <c r="C7" t="n">
-        <v>2703</v>
+        <v>2860</v>
       </c>
       <c r="D7" t="n">
-        <v>597</v>
+        <v>571</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>937</v>
+        <v>1165</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>255</v>
+        <v>286</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D11" t="n">
         <v>129</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2977</v>
+        <v>4575</v>
       </c>
       <c r="C2" t="n">
-        <v>9689</v>
+        <v>2978</v>
       </c>
       <c r="D2" t="n">
-        <v>16713</v>
+        <v>13680</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3189</v>
+        <v>3817</v>
       </c>
       <c r="C3" t="n">
-        <v>4302</v>
+        <v>3408</v>
       </c>
       <c r="D3" t="n">
-        <v>19264</v>
+        <v>13837</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3365</v>
+        <v>4191</v>
       </c>
       <c r="C4" t="n">
-        <v>6856</v>
+        <v>5140</v>
       </c>
       <c r="D4" t="n">
-        <v>15034</v>
+        <v>12211</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2172</v>
+        <v>2879</v>
       </c>
       <c r="C5" t="n">
-        <v>8768</v>
+        <v>5906</v>
       </c>
       <c r="D5" t="n">
-        <v>6774</v>
+        <v>5804</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1010</v>
+        <v>1449</v>
       </c>
       <c r="C6" t="n">
-        <v>7284</v>
+        <v>5253</v>
       </c>
       <c r="D6" t="n">
-        <v>1976</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>266</v>
+        <v>425</v>
       </c>
       <c r="C7" t="n">
-        <v>3807</v>
+        <v>3594</v>
       </c>
       <c r="D7" t="n">
-        <v>694</v>
+        <v>665</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="C8" t="n">
-        <v>1560</v>
+        <v>1830</v>
       </c>
       <c r="D8" t="n">
-        <v>397</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>469</v>
+        <v>575</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3103,7 +3103,7 @@
         <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
         <v>33</v>
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2085</v>
+        <v>3265</v>
       </c>
       <c r="C2" t="n">
-        <v>5474</v>
+        <v>2162</v>
       </c>
       <c r="D2" t="n">
-        <v>12039</v>
+        <v>10520</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2742</v>
+        <v>3561</v>
       </c>
       <c r="C3" t="n">
-        <v>5733</v>
+        <v>2960</v>
       </c>
       <c r="D3" t="n">
-        <v>17961</v>
+        <v>13065</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3054</v>
+        <v>3757</v>
       </c>
       <c r="C4" t="n">
-        <v>5930</v>
+        <v>4466</v>
       </c>
       <c r="D4" t="n">
-        <v>15249</v>
+        <v>12175</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2359</v>
+        <v>3109</v>
       </c>
       <c r="C5" t="n">
-        <v>8195</v>
+        <v>5673</v>
       </c>
       <c r="D5" t="n">
-        <v>7570</v>
+        <v>6477</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1178</v>
+        <v>1725</v>
       </c>
       <c r="C6" t="n">
-        <v>8021</v>
+        <v>5680</v>
       </c>
       <c r="D6" t="n">
-        <v>2359</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>236</v>
+        <v>398</v>
       </c>
       <c r="C7" t="n">
-        <v>4850</v>
+        <v>4261</v>
       </c>
       <c r="D7" t="n">
-        <v>781</v>
+        <v>750</v>
       </c>
     </row>
     <row r="8">
@@ -3352,10 +3352,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>2037</v>
+        <v>2307</v>
       </c>
       <c r="D8" t="n">
         <v>412</v>
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>521</v>
+        <v>693</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3352</v>
+        <v>6218</v>
       </c>
       <c r="C2" t="n">
-        <v>11101</v>
+        <v>5105</v>
       </c>
       <c r="D2" t="n">
-        <v>19808</v>
+        <v>17328</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2125</v>
+        <v>2903</v>
       </c>
       <c r="C3" t="n">
-        <v>5031</v>
+        <v>2358</v>
       </c>
       <c r="D3" t="n">
-        <v>16176</v>
+        <v>12007</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2589</v>
+        <v>3235</v>
       </c>
       <c r="C4" t="n">
-        <v>5727</v>
+        <v>3722</v>
       </c>
       <c r="D4" t="n">
-        <v>15149</v>
+        <v>11816</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2354</v>
+        <v>3041</v>
       </c>
       <c r="C5" t="n">
-        <v>7154</v>
+        <v>5056</v>
       </c>
       <c r="D5" t="n">
-        <v>8225</v>
+        <v>7100</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1437</v>
+        <v>2050</v>
       </c>
       <c r="C6" t="n">
-        <v>8020</v>
+        <v>5628</v>
       </c>
       <c r="D6" t="n">
-        <v>2979</v>
+        <v>2686</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>450</v>
+        <v>734</v>
       </c>
       <c r="C7" t="n">
-        <v>5966</v>
+        <v>4801</v>
       </c>
       <c r="D7" t="n">
-        <v>958</v>
+        <v>918</v>
       </c>
     </row>
     <row r="8">
@@ -3663,10 +3663,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="C8" t="n">
-        <v>2993</v>
+        <v>3037</v>
       </c>
       <c r="D8" t="n">
         <v>447</v>
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>986</v>
+        <v>1237</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>295</v>
+        <v>367</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>39</v>
+      </c>
+      <c r="D14" t="n">
         <v>37</v>
-      </c>
-      <c r="D14" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4491</v>
+        <v>9908</v>
       </c>
       <c r="C2" t="n">
-        <v>5653</v>
+        <v>7545</v>
       </c>
       <c r="D2" t="n">
-        <v>20082</v>
+        <v>8613</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2450</v>
+        <v>4400</v>
       </c>
       <c r="C2" t="n">
-        <v>6571</v>
+        <v>2859</v>
       </c>
       <c r="D2" t="n">
-        <v>14738</v>
+        <v>12753</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2934</v>
+        <v>4090</v>
       </c>
       <c r="C3" t="n">
-        <v>6807</v>
+        <v>3217</v>
       </c>
       <c r="D3" t="n">
-        <v>17801</v>
+        <v>13429</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3476</v>
+        <v>4433</v>
       </c>
       <c r="C4" t="n">
-        <v>8233</v>
+        <v>5349</v>
       </c>
       <c r="D4" t="n">
-        <v>15353</v>
+        <v>12185</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1349</v>
+        <v>2006</v>
       </c>
       <c r="C5" t="n">
-        <v>10987</v>
+        <v>7706</v>
       </c>
       <c r="D5" t="n">
-        <v>7410</v>
+        <v>6496</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>415</v>
+        <v>678</v>
       </c>
       <c r="C6" t="n">
-        <v>7182</v>
+        <v>5863</v>
       </c>
       <c r="D6" t="n">
-        <v>2256</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="C7" t="n">
-        <v>2933</v>
+        <v>2976</v>
       </c>
       <c r="D7" t="n">
-        <v>550</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>966</v>
+        <v>1212</v>
       </c>
       <c r="D8" t="n">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>289</v>
+        <v>359</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>38</v>
+      </c>
+      <c r="D13" t="n">
         <v>36</v>
-      </c>
-      <c r="D13" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6846</v>
+        <v>8375</v>
       </c>
       <c r="C2" t="n">
-        <v>4290</v>
+        <v>6155</v>
       </c>
       <c r="D2" t="n">
-        <v>20095</v>
+        <v>18842</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1909</v>
+        <v>4206</v>
       </c>
       <c r="C3" t="n">
-        <v>2849</v>
+        <v>3802</v>
       </c>
       <c r="D3" t="n">
-        <v>4013</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
         <v>816</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4421</v>
+        <v>5647</v>
       </c>
       <c r="C2" t="n">
-        <v>8711</v>
+        <v>9244</v>
       </c>
       <c r="D2" t="n">
-        <v>33739</v>
+        <v>18207</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3590</v>
+        <v>5172</v>
       </c>
       <c r="C3" t="n">
-        <v>3160</v>
+        <v>4427</v>
       </c>
       <c r="D3" t="n">
-        <v>6419</v>
+        <v>4747</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>863</v>
+        <v>1861</v>
       </c>
       <c r="C4" t="n">
-        <v>1714</v>
+        <v>2272</v>
       </c>
       <c r="D4" t="n">
-        <v>1990</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,7 +4882,7 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
         <v>859</v>
@@ -4896,7 +4896,7 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5910</v>
+        <v>7199</v>
       </c>
       <c r="C2" t="n">
-        <v>9007</v>
+        <v>8211</v>
       </c>
       <c r="D2" t="n">
-        <v>44807</v>
+        <v>29570</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3292</v>
+        <v>4460</v>
       </c>
       <c r="C3" t="n">
-        <v>5355</v>
+        <v>6074</v>
       </c>
       <c r="D3" t="n">
-        <v>10328</v>
+        <v>6558</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1888</v>
+        <v>2999</v>
       </c>
       <c r="C4" t="n">
-        <v>2497</v>
+        <v>3402</v>
       </c>
       <c r="D4" t="n">
-        <v>2779</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>407</v>
+        <v>807</v>
       </c>
       <c r="C5" t="n">
-        <v>1033</v>
+        <v>1339</v>
       </c>
       <c r="D5" t="n">
-        <v>1294</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
         <v>908</v>
@@ -5207,7 +5207,7 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
         <v>626</v>
@@ -5218,10 +5218,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
         <v>454</v>
@@ -5263,7 +5263,7 @@
         <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5827</v>
+        <v>7860</v>
       </c>
       <c r="C2" t="n">
-        <v>10605</v>
+        <v>6420</v>
       </c>
       <c r="D2" t="n">
-        <v>35081</v>
+        <v>35941</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3689</v>
+        <v>4701</v>
       </c>
       <c r="C3" t="n">
-        <v>6276</v>
+        <v>6236</v>
       </c>
       <c r="D3" t="n">
-        <v>14841</v>
+        <v>9594</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2174</v>
+        <v>3153</v>
       </c>
       <c r="C4" t="n">
-        <v>3930</v>
+        <v>4709</v>
       </c>
       <c r="D4" t="n">
-        <v>4071</v>
+        <v>2893</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>938</v>
+        <v>1574</v>
       </c>
       <c r="C5" t="n">
-        <v>1770</v>
+        <v>2380</v>
       </c>
       <c r="D5" t="n">
-        <v>1498</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>241</v>
+        <v>399</v>
       </c>
       <c r="C6" t="n">
-        <v>665</v>
+        <v>817</v>
       </c>
       <c r="D6" t="n">
-        <v>962</v>
+        <v>949</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5546,7 +5546,7 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
         <v>380</v>
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7476</v>
+        <v>8401</v>
       </c>
       <c r="C2" t="n">
-        <v>8358</v>
+        <v>3809</v>
       </c>
       <c r="D2" t="n">
-        <v>30668</v>
+        <v>38205</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3461</v>
+        <v>4498</v>
       </c>
       <c r="C3" t="n">
-        <v>6923</v>
+        <v>5188</v>
       </c>
       <c r="D3" t="n">
-        <v>15874</v>
+        <v>12157</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1792</v>
+        <v>2406</v>
       </c>
       <c r="C4" t="n">
-        <v>4225</v>
+        <v>4529</v>
       </c>
       <c r="D4" t="n">
-        <v>5162</v>
+        <v>3515</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>802</v>
+        <v>1239</v>
       </c>
       <c r="C5" t="n">
-        <v>2113</v>
+        <v>2587</v>
       </c>
       <c r="D5" t="n">
-        <v>1524</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>277</v>
+        <v>455</v>
       </c>
       <c r="C6" t="n">
-        <v>815</v>
+        <v>1070</v>
       </c>
       <c r="D6" t="n">
-        <v>801</v>
+        <v>762</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>318</v>
+        <v>365</v>
       </c>
       <c r="D7" t="n">
-        <v>515</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D10" t="n">
         <v>233</v>
@@ -5882,10 +5882,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
         <v>195</v>
@@ -5896,7 +5896,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
         <v>91</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5826</v>
+        <v>8369</v>
       </c>
       <c r="C2" t="n">
-        <v>10480</v>
+        <v>2366</v>
       </c>
       <c r="D2" t="n">
-        <v>26042</v>
+        <v>27464</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4525</v>
+        <v>5334</v>
       </c>
       <c r="C3" t="n">
-        <v>6671</v>
+        <v>3781</v>
       </c>
       <c r="D3" t="n">
-        <v>17191</v>
+        <v>15638</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2296</v>
+        <v>3017</v>
       </c>
       <c r="C4" t="n">
-        <v>5742</v>
+        <v>4827</v>
       </c>
       <c r="D4" t="n">
-        <v>7164</v>
+        <v>5150</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1141</v>
+        <v>1620</v>
       </c>
       <c r="C5" t="n">
-        <v>3285</v>
+        <v>3651</v>
       </c>
       <c r="D5" t="n">
-        <v>2161</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>498</v>
+        <v>772</v>
       </c>
       <c r="C6" t="n">
-        <v>1519</v>
+        <v>1901</v>
       </c>
       <c r="D6" t="n">
-        <v>928</v>
+        <v>847</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>162</v>
+        <v>255</v>
       </c>
       <c r="C7" t="n">
-        <v>595</v>
+        <v>748</v>
       </c>
       <c r="D7" t="n">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>273</v>
+        <v>299</v>
       </c>
       <c r="D8" t="n">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
         <v>153</v>
@@ -6221,7 +6221,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
         <v>80</v>
@@ -6238,7 +6238,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5101</v>
+        <v>6786</v>
       </c>
       <c r="C2" t="n">
-        <v>9302</v>
+        <v>5631</v>
       </c>
       <c r="D2" t="n">
-        <v>26830</v>
+        <v>23578</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4241</v>
+        <v>5576</v>
       </c>
       <c r="C3" t="n">
-        <v>7532</v>
+        <v>2639</v>
       </c>
       <c r="D3" t="n">
-        <v>17326</v>
+        <v>16334</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2906</v>
+        <v>3569</v>
       </c>
       <c r="C4" t="n">
-        <v>6075</v>
+        <v>4107</v>
       </c>
       <c r="D4" t="n">
-        <v>8706</v>
+        <v>6857</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1479</v>
+        <v>2005</v>
       </c>
       <c r="C5" t="n">
-        <v>4537</v>
+        <v>4207</v>
       </c>
       <c r="D5" t="n">
-        <v>3007</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>736</v>
+        <v>1080</v>
       </c>
       <c r="C6" t="n">
-        <v>2417</v>
+        <v>2786</v>
       </c>
       <c r="D6" t="n">
-        <v>1119</v>
+        <v>965</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>284</v>
+        <v>443</v>
       </c>
       <c r="C7" t="n">
-        <v>1059</v>
+        <v>1327</v>
       </c>
       <c r="D7" t="n">
-        <v>621</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="C8" t="n">
-        <v>433</v>
+        <v>523</v>
       </c>
       <c r="D8" t="n">
-        <v>406</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
         <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
         <v>158</v>
@@ -6535,7 +6535,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
         <v>121</v>
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>

--- a/output/yearly_population_iteration_57_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_57_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7056</v>
+        <v>7927</v>
       </c>
       <c r="C2" t="n">
-        <v>5773</v>
+        <v>6009</v>
       </c>
       <c r="D2" t="n">
-        <v>23335</v>
+        <v>31281</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5049</v>
+        <v>4533</v>
       </c>
       <c r="C3" t="n">
-        <v>3578</v>
+        <v>4112</v>
       </c>
       <c r="D3" t="n">
-        <v>16253</v>
+        <v>17360</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3823</v>
+        <v>3348</v>
       </c>
       <c r="C4" t="n">
-        <v>3274</v>
+        <v>5232</v>
       </c>
       <c r="D4" t="n">
-        <v>8286</v>
+        <v>8385</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2400</v>
+        <v>2173</v>
       </c>
       <c r="C5" t="n">
-        <v>4030</v>
+        <v>3976</v>
       </c>
       <c r="D5" t="n">
-        <v>2899</v>
+        <v>3106</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1358</v>
+        <v>1252</v>
       </c>
       <c r="C6" t="n">
-        <v>3439</v>
+        <v>2547</v>
       </c>
       <c r="D6" t="n">
-        <v>1159</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>648</v>
+        <v>604</v>
       </c>
       <c r="C7" t="n">
-        <v>1999</v>
+        <v>1553</v>
       </c>
       <c r="D7" t="n">
-        <v>649</v>
+        <v>661</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="C8" t="n">
-        <v>893</v>
+        <v>730</v>
       </c>
       <c r="D8" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>371</v>
+        <v>328</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -895,7 +895,7 @@
         <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D10" t="n">
         <v>244</v>
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1052,7 +1052,7 @@
         <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9098</v>
+        <v>8808</v>
       </c>
       <c r="C2" t="n">
-        <v>9311</v>
+        <v>9636</v>
       </c>
       <c r="D2" t="n">
-        <v>27930</v>
+        <v>31555</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4852</v>
+        <v>4878</v>
       </c>
       <c r="C3" t="n">
-        <v>4014</v>
+        <v>4377</v>
       </c>
       <c r="D3" t="n">
-        <v>16123</v>
+        <v>18086</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3750</v>
+        <v>3294</v>
       </c>
       <c r="C4" t="n">
-        <v>3348</v>
+        <v>4585</v>
       </c>
       <c r="D4" t="n">
-        <v>9334</v>
+        <v>9594</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2645</v>
+        <v>2365</v>
       </c>
       <c r="C5" t="n">
-        <v>3566</v>
+        <v>4433</v>
       </c>
       <c r="D5" t="n">
-        <v>3610</v>
+        <v>3792</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1633</v>
+        <v>1511</v>
       </c>
       <c r="C6" t="n">
-        <v>3666</v>
+        <v>3166</v>
       </c>
       <c r="D6" t="n">
-        <v>1410</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>853</v>
+        <v>785</v>
       </c>
       <c r="C7" t="n">
-        <v>2599</v>
+        <v>1975</v>
       </c>
       <c r="D7" t="n">
-        <v>710</v>
+        <v>728</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>356</v>
+        <v>331</v>
       </c>
       <c r="C8" t="n">
-        <v>1358</v>
+        <v>1084</v>
       </c>
       <c r="D8" t="n">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C9" t="n">
-        <v>576</v>
+        <v>490</v>
       </c>
       <c r="D9" t="n">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1217,7 +1217,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
         <v>180</v>
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
         <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1363,7 +1363,7 @@
         <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9484</v>
+        <v>9343</v>
       </c>
       <c r="C2" t="n">
-        <v>7638</v>
+        <v>10023</v>
       </c>
       <c r="D2" t="n">
-        <v>24340</v>
+        <v>30341</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5297</v>
+        <v>5254</v>
       </c>
       <c r="C3" t="n">
-        <v>5509</v>
+        <v>5780</v>
       </c>
       <c r="D3" t="n">
-        <v>16507</v>
+        <v>18544</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3574</v>
+        <v>3347</v>
       </c>
       <c r="C4" t="n">
-        <v>3527</v>
+        <v>4355</v>
       </c>
       <c r="D4" t="n">
-        <v>9938</v>
+        <v>10433</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2738</v>
+        <v>2458</v>
       </c>
       <c r="C5" t="n">
-        <v>3367</v>
+        <v>4362</v>
       </c>
       <c r="D5" t="n">
-        <v>4324</v>
+        <v>4512</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1851</v>
+        <v>1686</v>
       </c>
       <c r="C6" t="n">
-        <v>3593</v>
+        <v>3660</v>
       </c>
       <c r="D6" t="n">
-        <v>1673</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1048</v>
+        <v>960</v>
       </c>
       <c r="C7" t="n">
-        <v>2990</v>
+        <v>2433</v>
       </c>
       <c r="D7" t="n">
-        <v>798</v>
+        <v>817</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>479</v>
+        <v>447</v>
       </c>
       <c r="C8" t="n">
-        <v>1818</v>
+        <v>1422</v>
       </c>
       <c r="D8" t="n">
-        <v>476</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C9" t="n">
-        <v>866</v>
+        <v>716</v>
       </c>
       <c r="D9" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C10" t="n">
-        <v>377</v>
+        <v>338</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1674,7 +1674,7 @@
         <v>109</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8773</v>
+        <v>8650</v>
       </c>
       <c r="C2" t="n">
-        <v>5254</v>
+        <v>6815</v>
       </c>
       <c r="D2" t="n">
-        <v>20264</v>
+        <v>24984</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6384</v>
+        <v>6164</v>
       </c>
       <c r="C3" t="n">
-        <v>7600</v>
+        <v>8549</v>
       </c>
       <c r="D3" t="n">
-        <v>18107</v>
+        <v>20295</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2529</v>
+        <v>2271</v>
       </c>
       <c r="C4" t="n">
-        <v>5162</v>
+        <v>6570</v>
       </c>
       <c r="D4" t="n">
-        <v>9476</v>
+        <v>9929</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1710</v>
+        <v>1557</v>
       </c>
       <c r="C5" t="n">
-        <v>3521</v>
+        <v>3586</v>
       </c>
       <c r="D5" t="n">
-        <v>2801</v>
+        <v>2938</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>968</v>
+        <v>887</v>
       </c>
       <c r="C6" t="n">
-        <v>2930</v>
+        <v>2384</v>
       </c>
       <c r="D6" t="n">
-        <v>782</v>
+        <v>800</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>442</v>
+        <v>413</v>
       </c>
       <c r="C7" t="n">
-        <v>1781</v>
+        <v>1393</v>
       </c>
       <c r="D7" t="n">
-        <v>466</v>
+        <v>478</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="C8" t="n">
-        <v>848</v>
+        <v>701</v>
       </c>
       <c r="D8" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C9" t="n">
-        <v>369</v>
+        <v>331</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1971,7 +1971,7 @@
         <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5452</v>
+        <v>5348</v>
       </c>
       <c r="C2" t="n">
-        <v>2573</v>
+        <v>3025</v>
       </c>
       <c r="D2" t="n">
-        <v>13731</v>
+        <v>17226</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6397</v>
+        <v>6234</v>
       </c>
       <c r="C3" t="n">
-        <v>5937</v>
+        <v>7020</v>
       </c>
       <c r="D3" t="n">
-        <v>17531</v>
+        <v>19763</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3465</v>
+        <v>3236</v>
       </c>
       <c r="C4" t="n">
-        <v>6376</v>
+        <v>7616</v>
       </c>
       <c r="D4" t="n">
-        <v>10521</v>
+        <v>11410</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1913</v>
+        <v>1720</v>
       </c>
       <c r="C5" t="n">
-        <v>4244</v>
+        <v>4915</v>
       </c>
       <c r="D5" t="n">
-        <v>3602</v>
+        <v>3777</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1148</v>
+        <v>1062</v>
       </c>
       <c r="C6" t="n">
-        <v>3312</v>
+        <v>2921</v>
       </c>
       <c r="D6" t="n">
-        <v>989</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>412</v>
+        <v>389</v>
       </c>
       <c r="C7" t="n">
-        <v>2223</v>
+        <v>1787</v>
       </c>
       <c r="D7" t="n">
-        <v>510</v>
+        <v>523</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>1131</v>
+        <v>914</v>
       </c>
       <c r="D8" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>413</v>
+        <v>384</v>
       </c>
       <c r="D9" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
         <v>210</v>
@@ -2150,10 +2150,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>167</v>
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2268,7 +2268,7 @@
         <v>106</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6035</v>
+        <v>6525</v>
       </c>
       <c r="C2" t="n">
-        <v>6369</v>
+        <v>4876</v>
       </c>
       <c r="D2" t="n">
-        <v>14955</v>
+        <v>14618</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5036</v>
+        <v>4920</v>
       </c>
       <c r="C3" t="n">
-        <v>3863</v>
+        <v>4560</v>
       </c>
       <c r="D3" t="n">
-        <v>15945</v>
+        <v>18227</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4089</v>
+        <v>3912</v>
       </c>
       <c r="C4" t="n">
-        <v>6028</v>
+        <v>7165</v>
       </c>
       <c r="D4" t="n">
-        <v>11345</v>
+        <v>12426</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2282</v>
+        <v>2092</v>
       </c>
       <c r="C5" t="n">
-        <v>5158</v>
+        <v>6083</v>
       </c>
       <c r="D5" t="n">
-        <v>4555</v>
+        <v>4834</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1347</v>
+        <v>1229</v>
       </c>
       <c r="C6" t="n">
-        <v>3732</v>
+        <v>3820</v>
       </c>
       <c r="D6" t="n">
-        <v>1352</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>620</v>
+        <v>579</v>
       </c>
       <c r="C7" t="n">
-        <v>2713</v>
+        <v>2292</v>
       </c>
       <c r="D7" t="n">
-        <v>570</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="C8" t="n">
-        <v>1580</v>
+        <v>1273</v>
       </c>
       <c r="D8" t="n">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -2436,10 +2436,10 @@
         <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>684</v>
+        <v>584</v>
       </c>
       <c r="D9" t="n">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="D10" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11">
@@ -2461,7 +2461,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
         <v>184</v>
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2579,7 +2579,7 @@
         <v>58</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3618</v>
+        <v>3877</v>
       </c>
       <c r="C2" t="n">
-        <v>3000</v>
+        <v>2313</v>
       </c>
       <c r="D2" t="n">
-        <v>10325</v>
+        <v>10103</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5090</v>
+        <v>5118</v>
       </c>
       <c r="C3" t="n">
-        <v>4550</v>
+        <v>4483</v>
       </c>
       <c r="D3" t="n">
-        <v>15604</v>
+        <v>17560</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4506</v>
+        <v>4306</v>
       </c>
       <c r="C4" t="n">
-        <v>5811</v>
+        <v>6897</v>
       </c>
       <c r="D4" t="n">
-        <v>11985</v>
+        <v>13192</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2383</v>
+        <v>2182</v>
       </c>
       <c r="C5" t="n">
-        <v>6110</v>
+        <v>7189</v>
       </c>
       <c r="D5" t="n">
-        <v>4801</v>
+        <v>5103</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1120</v>
+        <v>1034</v>
       </c>
       <c r="C6" t="n">
-        <v>4622</v>
+        <v>4625</v>
       </c>
       <c r="D6" t="n">
-        <v>1318</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="C7" t="n">
-        <v>2860</v>
+        <v>2375</v>
       </c>
       <c r="D7" t="n">
-        <v>571</v>
+        <v>583</v>
       </c>
     </row>
     <row r="8">
@@ -2733,10 +2733,10 @@
         <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>1165</v>
+        <v>971</v>
       </c>
       <c r="D8" t="n">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -2758,7 +2758,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
         <v>180</v>
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2876,7 +2876,7 @@
         <v>56</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4575</v>
+        <v>4100</v>
       </c>
       <c r="C2" t="n">
-        <v>2978</v>
+        <v>1904</v>
       </c>
       <c r="D2" t="n">
-        <v>13680</v>
+        <v>12973</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3817</v>
+        <v>3887</v>
       </c>
       <c r="C3" t="n">
-        <v>3408</v>
+        <v>3095</v>
       </c>
       <c r="D3" t="n">
-        <v>13837</v>
+        <v>15365</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4191</v>
+        <v>4092</v>
       </c>
       <c r="C4" t="n">
-        <v>5140</v>
+        <v>5661</v>
       </c>
       <c r="D4" t="n">
-        <v>12211</v>
+        <v>13503</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2879</v>
+        <v>2691</v>
       </c>
       <c r="C5" t="n">
-        <v>5906</v>
+        <v>6976</v>
       </c>
       <c r="D5" t="n">
-        <v>5804</v>
+        <v>6239</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1449</v>
+        <v>1342</v>
       </c>
       <c r="C6" t="n">
-        <v>5253</v>
+        <v>5710</v>
       </c>
       <c r="D6" t="n">
-        <v>1768</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>425</v>
+        <v>386</v>
       </c>
       <c r="C7" t="n">
-        <v>3594</v>
+        <v>3324</v>
       </c>
       <c r="D7" t="n">
-        <v>665</v>
+        <v>682</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>1830</v>
+        <v>1498</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>575</v>
+        <v>508</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -3069,10 +3069,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
         <v>174</v>
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
         <v>33</v>
@@ -3173,7 +3173,7 @@
         <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3265</v>
+        <v>2923</v>
       </c>
       <c r="C2" t="n">
-        <v>2162</v>
+        <v>2291</v>
       </c>
       <c r="D2" t="n">
-        <v>10520</v>
+        <v>10314</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3561</v>
+        <v>3465</v>
       </c>
       <c r="C3" t="n">
-        <v>2960</v>
+        <v>2379</v>
       </c>
       <c r="D3" t="n">
-        <v>13065</v>
+        <v>14242</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3757</v>
+        <v>3711</v>
       </c>
       <c r="C4" t="n">
-        <v>4466</v>
+        <v>4647</v>
       </c>
       <c r="D4" t="n">
-        <v>12175</v>
+        <v>13472</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3109</v>
+        <v>2965</v>
       </c>
       <c r="C5" t="n">
-        <v>5673</v>
+        <v>6619</v>
       </c>
       <c r="D5" t="n">
-        <v>6477</v>
+        <v>7005</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1725</v>
+        <v>1579</v>
       </c>
       <c r="C6" t="n">
-        <v>5680</v>
+        <v>6339</v>
       </c>
       <c r="D6" t="n">
-        <v>2130</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>398</v>
+        <v>360</v>
       </c>
       <c r="C7" t="n">
-        <v>4261</v>
+        <v>4135</v>
       </c>
       <c r="D7" t="n">
-        <v>750</v>
+        <v>782</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>2307</v>
+        <v>1935</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>693</v>
+        <v>594</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
         <v>62</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3470,7 +3470,7 @@
         <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6218</v>
+        <v>4605</v>
       </c>
       <c r="C2" t="n">
-        <v>5105</v>
+        <v>10257</v>
       </c>
       <c r="D2" t="n">
-        <v>17328</v>
+        <v>13565</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2903</v>
+        <v>2754</v>
       </c>
       <c r="C3" t="n">
-        <v>2358</v>
+        <v>2080</v>
       </c>
       <c r="D3" t="n">
-        <v>12007</v>
+        <v>12859</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3235</v>
+        <v>3149</v>
       </c>
       <c r="C4" t="n">
-        <v>3722</v>
+        <v>3570</v>
       </c>
       <c r="D4" t="n">
-        <v>11816</v>
+        <v>13173</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3041</v>
+        <v>2937</v>
       </c>
       <c r="C5" t="n">
-        <v>5056</v>
+        <v>5667</v>
       </c>
       <c r="D5" t="n">
-        <v>7100</v>
+        <v>7593</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2050</v>
+        <v>1912</v>
       </c>
       <c r="C6" t="n">
-        <v>5628</v>
+        <v>6394</v>
       </c>
       <c r="D6" t="n">
-        <v>2686</v>
+        <v>2853</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>734</v>
+        <v>669</v>
       </c>
       <c r="C7" t="n">
-        <v>4801</v>
+        <v>5016</v>
       </c>
       <c r="D7" t="n">
-        <v>918</v>
+        <v>960</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C8" t="n">
-        <v>3037</v>
+        <v>2710</v>
       </c>
       <c r="D8" t="n">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>1237</v>
+        <v>1046</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>367</v>
+        <v>336</v>
       </c>
       <c r="D10" t="n">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
         <v>63</v>
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
         <v>37</v>
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9908</v>
+        <v>7575</v>
       </c>
       <c r="C2" t="n">
-        <v>7545</v>
+        <v>5184</v>
       </c>
       <c r="D2" t="n">
-        <v>8613</v>
+        <v>7225</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4400</v>
+        <v>3298</v>
       </c>
       <c r="C2" t="n">
-        <v>2859</v>
+        <v>5826</v>
       </c>
       <c r="D2" t="n">
-        <v>12753</v>
+        <v>9983</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4090</v>
+        <v>3744</v>
       </c>
       <c r="C3" t="n">
-        <v>3217</v>
+        <v>4156</v>
       </c>
       <c r="D3" t="n">
-        <v>13429</v>
+        <v>14098</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4433</v>
+        <v>4322</v>
       </c>
       <c r="C4" t="n">
-        <v>5349</v>
+        <v>5387</v>
       </c>
       <c r="D4" t="n">
-        <v>12185</v>
+        <v>13510</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2006</v>
+        <v>1848</v>
       </c>
       <c r="C5" t="n">
-        <v>7706</v>
+        <v>8649</v>
       </c>
       <c r="D5" t="n">
-        <v>6496</v>
+        <v>6937</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>678</v>
+        <v>618</v>
       </c>
       <c r="C6" t="n">
-        <v>5863</v>
+        <v>6231</v>
       </c>
       <c r="D6" t="n">
-        <v>2098</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="C7" t="n">
-        <v>2976</v>
+        <v>2655</v>
       </c>
       <c r="D7" t="n">
-        <v>555</v>
+        <v>563</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>1212</v>
+        <v>1025</v>
       </c>
       <c r="D8" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>359</v>
+        <v>329</v>
       </c>
       <c r="D9" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
         <v>61</v>
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
         <v>36</v>
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8375</v>
+        <v>8382</v>
       </c>
       <c r="C2" t="n">
-        <v>6155</v>
+        <v>5364</v>
       </c>
       <c r="D2" t="n">
-        <v>18842</v>
+        <v>22709</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4206</v>
+        <v>3217</v>
       </c>
       <c r="C3" t="n">
-        <v>3802</v>
+        <v>2612</v>
       </c>
       <c r="D3" t="n">
-        <v>2086</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5647</v>
+        <v>5853</v>
       </c>
       <c r="C2" t="n">
-        <v>9244</v>
+        <v>6907</v>
       </c>
       <c r="D2" t="n">
-        <v>18207</v>
+        <v>23514</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5172</v>
+        <v>4762</v>
       </c>
       <c r="C3" t="n">
-        <v>4427</v>
+        <v>3595</v>
       </c>
       <c r="D3" t="n">
-        <v>4747</v>
+        <v>5220</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1861</v>
+        <v>1432</v>
       </c>
       <c r="C4" t="n">
-        <v>2272</v>
+        <v>1574</v>
       </c>
       <c r="D4" t="n">
-        <v>1601</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>853</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7199</v>
+        <v>6194</v>
       </c>
       <c r="C2" t="n">
-        <v>8211</v>
+        <v>4897</v>
       </c>
       <c r="D2" t="n">
-        <v>29570</v>
+        <v>30211</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4460</v>
+        <v>4363</v>
       </c>
       <c r="C3" t="n">
-        <v>6074</v>
+        <v>4675</v>
       </c>
       <c r="D3" t="n">
-        <v>6558</v>
+        <v>7771</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2999</v>
+        <v>2634</v>
       </c>
       <c r="C4" t="n">
-        <v>3402</v>
+        <v>2685</v>
       </c>
       <c r="D4" t="n">
-        <v>2156</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>807</v>
+        <v>635</v>
       </c>
       <c r="C5" t="n">
-        <v>1339</v>
+        <v>955</v>
       </c>
       <c r="D5" t="n">
-        <v>1223</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="6">
@@ -5196,7 +5196,7 @@
         <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>903</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5246,7 +5246,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
         <v>210</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7860</v>
+        <v>6355</v>
       </c>
       <c r="C2" t="n">
-        <v>6420</v>
+        <v>4815</v>
       </c>
       <c r="D2" t="n">
-        <v>35941</v>
+        <v>33299</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4701</v>
+        <v>4336</v>
       </c>
       <c r="C3" t="n">
-        <v>6236</v>
+        <v>4168</v>
       </c>
       <c r="D3" t="n">
-        <v>9594</v>
+        <v>10634</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3153</v>
+        <v>2944</v>
       </c>
       <c r="C4" t="n">
-        <v>4709</v>
+        <v>3698</v>
       </c>
       <c r="D4" t="n">
-        <v>2893</v>
+        <v>3157</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1574</v>
+        <v>1338</v>
       </c>
       <c r="C5" t="n">
-        <v>2380</v>
+        <v>1831</v>
       </c>
       <c r="D5" t="n">
-        <v>1335</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>399</v>
+        <v>337</v>
       </c>
       <c r="C6" t="n">
-        <v>817</v>
+        <v>622</v>
       </c>
       <c r="D6" t="n">
-        <v>949</v>
+        <v>944</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>662</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
         <v>342</v>
@@ -5574,7 +5574,7 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5585,7 +5585,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
         <v>158</v>
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8401</v>
+        <v>7529</v>
       </c>
       <c r="C2" t="n">
-        <v>3809</v>
+        <v>9932</v>
       </c>
       <c r="D2" t="n">
-        <v>38205</v>
+        <v>29787</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4498</v>
+        <v>3867</v>
       </c>
       <c r="C3" t="n">
-        <v>5188</v>
+        <v>3685</v>
       </c>
       <c r="D3" t="n">
-        <v>12157</v>
+        <v>12541</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2406</v>
+        <v>2245</v>
       </c>
       <c r="C4" t="n">
-        <v>4529</v>
+        <v>3241</v>
       </c>
       <c r="D4" t="n">
-        <v>3515</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1239</v>
+        <v>1124</v>
       </c>
       <c r="C5" t="n">
-        <v>2587</v>
+        <v>2033</v>
       </c>
       <c r="D5" t="n">
-        <v>1266</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>455</v>
+        <v>391</v>
       </c>
       <c r="C6" t="n">
-        <v>1070</v>
+        <v>829</v>
       </c>
       <c r="D6" t="n">
-        <v>762</v>
+        <v>769</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C7" t="n">
-        <v>365</v>
+        <v>310</v>
       </c>
       <c r="D7" t="n">
-        <v>522</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
         <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
         <v>117</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8369</v>
+        <v>6904</v>
       </c>
       <c r="C2" t="n">
-        <v>2366</v>
+        <v>6908</v>
       </c>
       <c r="D2" t="n">
-        <v>27464</v>
+        <v>33470</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5334</v>
+        <v>4740</v>
       </c>
       <c r="C3" t="n">
-        <v>3781</v>
+        <v>6314</v>
       </c>
       <c r="D3" t="n">
-        <v>15638</v>
+        <v>14515</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3017</v>
+        <v>2683</v>
       </c>
       <c r="C4" t="n">
-        <v>4827</v>
+        <v>3442</v>
       </c>
       <c r="D4" t="n">
-        <v>5150</v>
+        <v>5457</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1620</v>
+        <v>1505</v>
       </c>
       <c r="C5" t="n">
-        <v>3651</v>
+        <v>2698</v>
       </c>
       <c r="D5" t="n">
-        <v>1647</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>772</v>
+        <v>696</v>
       </c>
       <c r="C6" t="n">
-        <v>1901</v>
+        <v>1492</v>
       </c>
       <c r="D6" t="n">
-        <v>847</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>255</v>
+        <v>225</v>
       </c>
       <c r="C7" t="n">
-        <v>748</v>
+        <v>604</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>551</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>299</v>
+        <v>269</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6171,7 +6171,7 @@
         <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6786</v>
+        <v>6390</v>
       </c>
       <c r="C2" t="n">
-        <v>5631</v>
+        <v>3647</v>
       </c>
       <c r="D2" t="n">
-        <v>23578</v>
+        <v>30346</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5576</v>
+        <v>4765</v>
       </c>
       <c r="C3" t="n">
-        <v>2639</v>
+        <v>5745</v>
       </c>
       <c r="D3" t="n">
-        <v>16334</v>
+        <v>16502</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3569</v>
+        <v>3190</v>
       </c>
       <c r="C4" t="n">
-        <v>4107</v>
+        <v>4997</v>
       </c>
       <c r="D4" t="n">
-        <v>6857</v>
+        <v>7030</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2005</v>
+        <v>1825</v>
       </c>
       <c r="C5" t="n">
-        <v>4207</v>
+        <v>3048</v>
       </c>
       <c r="D5" t="n">
-        <v>2235</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1080</v>
+        <v>999</v>
       </c>
       <c r="C6" t="n">
-        <v>2786</v>
+        <v>2111</v>
       </c>
       <c r="D6" t="n">
-        <v>965</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>443</v>
+        <v>401</v>
       </c>
       <c r="C7" t="n">
-        <v>1327</v>
+        <v>1059</v>
       </c>
       <c r="D7" t="n">
-        <v>605</v>
+        <v>599</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>523</v>
+        <v>439</v>
       </c>
       <c r="D8" t="n">
-        <v>397</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="D9" t="n">
         <v>295</v>
@@ -6490,10 +6490,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
         <v>239</v>
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6650,7 +6650,7 @@
         <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_57_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_57_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7927</v>
+        <v>1200</v>
       </c>
       <c r="C2" t="n">
-        <v>6009</v>
+        <v>2392</v>
       </c>
       <c r="D2" t="n">
-        <v>31281</v>
+        <v>21222</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4533</v>
+        <v>2021</v>
       </c>
       <c r="C3" t="n">
-        <v>4112</v>
+        <v>6623</v>
       </c>
       <c r="D3" t="n">
-        <v>17360</v>
+        <v>16906</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3348</v>
+        <v>1175</v>
       </c>
       <c r="C4" t="n">
-        <v>5232</v>
+        <v>8683</v>
       </c>
       <c r="D4" t="n">
-        <v>8385</v>
+        <v>7124</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2173</v>
+        <v>535</v>
       </c>
       <c r="C5" t="n">
-        <v>3976</v>
+        <v>4871</v>
       </c>
       <c r="D5" t="n">
-        <v>3106</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1252</v>
+        <v>238</v>
       </c>
       <c r="C6" t="n">
-        <v>2547</v>
+        <v>2042</v>
       </c>
       <c r="D6" t="n">
-        <v>1211</v>
+        <v>753</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>604</v>
+        <v>97</v>
       </c>
       <c r="C7" t="n">
-        <v>1553</v>
+        <v>776</v>
       </c>
       <c r="D7" t="n">
-        <v>661</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>218</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>730</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>426</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>328</v>
+        <v>281</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>141</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8808</v>
+        <v>968</v>
       </c>
       <c r="C2" t="n">
-        <v>9636</v>
+        <v>5322</v>
       </c>
       <c r="D2" t="n">
-        <v>31555</v>
+        <v>20962</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4878</v>
+        <v>1381</v>
       </c>
       <c r="C3" t="n">
-        <v>4377</v>
+        <v>3888</v>
       </c>
       <c r="D3" t="n">
-        <v>18086</v>
+        <v>16371</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3294</v>
+        <v>1362</v>
       </c>
       <c r="C4" t="n">
-        <v>4585</v>
+        <v>7394</v>
       </c>
       <c r="D4" t="n">
-        <v>9594</v>
+        <v>8691</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2365</v>
+        <v>732</v>
       </c>
       <c r="C5" t="n">
-        <v>4433</v>
+        <v>6792</v>
       </c>
       <c r="D5" t="n">
-        <v>3792</v>
+        <v>2893</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1511</v>
+        <v>333</v>
       </c>
       <c r="C6" t="n">
-        <v>3166</v>
+        <v>3425</v>
       </c>
       <c r="D6" t="n">
-        <v>1485</v>
+        <v>960</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>785</v>
+        <v>140</v>
       </c>
       <c r="C7" t="n">
-        <v>1975</v>
+        <v>1378</v>
       </c>
       <c r="D7" t="n">
-        <v>728</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>331</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>1084</v>
+        <v>545</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>490</v>
+        <v>318</v>
       </c>
       <c r="D9" t="n">
         <v>318</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9343</v>
+        <v>523</v>
       </c>
       <c r="C2" t="n">
-        <v>10023</v>
+        <v>2226</v>
       </c>
       <c r="D2" t="n">
-        <v>30341</v>
+        <v>14270</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5254</v>
+        <v>1220</v>
       </c>
       <c r="C3" t="n">
-        <v>5780</v>
+        <v>4283</v>
       </c>
       <c r="D3" t="n">
-        <v>18544</v>
+        <v>16502</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3347</v>
+        <v>1480</v>
       </c>
       <c r="C4" t="n">
-        <v>4355</v>
+        <v>6674</v>
       </c>
       <c r="D4" t="n">
-        <v>10433</v>
+        <v>9654</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2458</v>
+        <v>728</v>
       </c>
       <c r="C5" t="n">
-        <v>4362</v>
+        <v>7818</v>
       </c>
       <c r="D5" t="n">
-        <v>4512</v>
+        <v>3279</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1686</v>
+        <v>277</v>
       </c>
       <c r="C6" t="n">
-        <v>3660</v>
+        <v>4353</v>
       </c>
       <c r="D6" t="n">
-        <v>1761</v>
+        <v>974</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>960</v>
+        <v>71</v>
       </c>
       <c r="C7" t="n">
-        <v>2433</v>
+        <v>1319</v>
       </c>
       <c r="D7" t="n">
-        <v>817</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>447</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1422</v>
+        <v>498</v>
       </c>
       <c r="D8" t="n">
-        <v>488</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>171</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>716</v>
+        <v>236</v>
       </c>
       <c r="D9" t="n">
-        <v>329</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>338</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>206</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8650</v>
+        <v>358</v>
       </c>
       <c r="C2" t="n">
-        <v>6815</v>
+        <v>3865</v>
       </c>
       <c r="D2" t="n">
-        <v>24984</v>
+        <v>13095</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6164</v>
+        <v>780</v>
       </c>
       <c r="C3" t="n">
-        <v>8549</v>
+        <v>2870</v>
       </c>
       <c r="D3" t="n">
-        <v>20295</v>
+        <v>15045</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2271</v>
+        <v>1216</v>
       </c>
       <c r="C4" t="n">
-        <v>6570</v>
+        <v>5359</v>
       </c>
       <c r="D4" t="n">
-        <v>9929</v>
+        <v>10543</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1557</v>
+        <v>929</v>
       </c>
       <c r="C5" t="n">
-        <v>3586</v>
+        <v>7170</v>
       </c>
       <c r="D5" t="n">
-        <v>2938</v>
+        <v>4219</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>887</v>
+        <v>414</v>
       </c>
       <c r="C6" t="n">
-        <v>2384</v>
+        <v>5991</v>
       </c>
       <c r="D6" t="n">
-        <v>800</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>413</v>
+        <v>126</v>
       </c>
       <c r="C7" t="n">
-        <v>1393</v>
+        <v>2652</v>
       </c>
       <c r="D7" t="n">
-        <v>478</v>
+        <v>609</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>158</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>701</v>
+        <v>829</v>
       </c>
       <c r="D8" t="n">
-        <v>322</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5348</v>
+        <v>287</v>
       </c>
       <c r="C2" t="n">
-        <v>3025</v>
+        <v>3541</v>
       </c>
       <c r="D2" t="n">
-        <v>17226</v>
+        <v>10362</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6234</v>
+        <v>550</v>
       </c>
       <c r="C3" t="n">
-        <v>7020</v>
+        <v>3006</v>
       </c>
       <c r="D3" t="n">
-        <v>19763</v>
+        <v>14057</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3236</v>
+        <v>982</v>
       </c>
       <c r="C4" t="n">
-        <v>7616</v>
+        <v>4278</v>
       </c>
       <c r="D4" t="n">
-        <v>11410</v>
+        <v>10971</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1720</v>
+        <v>992</v>
       </c>
       <c r="C5" t="n">
-        <v>4915</v>
+        <v>6565</v>
       </c>
       <c r="D5" t="n">
-        <v>3777</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1062</v>
+        <v>518</v>
       </c>
       <c r="C6" t="n">
-        <v>2921</v>
+        <v>6646</v>
       </c>
       <c r="D6" t="n">
-        <v>1019</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>389</v>
+        <v>137</v>
       </c>
       <c r="C7" t="n">
-        <v>1787</v>
+        <v>3781</v>
       </c>
       <c r="D7" t="n">
-        <v>523</v>
+        <v>674</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>914</v>
+        <v>1270</v>
       </c>
       <c r="D8" t="n">
-        <v>337</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>384</v>
+        <v>428</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6525</v>
+        <v>1430</v>
       </c>
       <c r="C2" t="n">
-        <v>4876</v>
+        <v>3849</v>
       </c>
       <c r="D2" t="n">
-        <v>14618</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4920</v>
+        <v>375</v>
       </c>
       <c r="C3" t="n">
-        <v>4560</v>
+        <v>2888</v>
       </c>
       <c r="D3" t="n">
-        <v>18227</v>
+        <v>12609</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3912</v>
+        <v>706</v>
       </c>
       <c r="C4" t="n">
-        <v>7165</v>
+        <v>3590</v>
       </c>
       <c r="D4" t="n">
-        <v>12426</v>
+        <v>11141</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2092</v>
+        <v>913</v>
       </c>
       <c r="C5" t="n">
-        <v>6083</v>
+        <v>5396</v>
       </c>
       <c r="D5" t="n">
-        <v>4834</v>
+        <v>5732</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1229</v>
+        <v>646</v>
       </c>
       <c r="C6" t="n">
-        <v>3820</v>
+        <v>6613</v>
       </c>
       <c r="D6" t="n">
-        <v>1402</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>579</v>
+        <v>243</v>
       </c>
       <c r="C7" t="n">
-        <v>2292</v>
+        <v>4958</v>
       </c>
       <c r="D7" t="n">
-        <v>585</v>
+        <v>795</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>194</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>1273</v>
+        <v>2266</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>584</v>
+        <v>737</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>384</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3877</v>
+        <v>972</v>
       </c>
       <c r="C2" t="n">
-        <v>2313</v>
+        <v>2033</v>
       </c>
       <c r="D2" t="n">
-        <v>10103</v>
+        <v>7966</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5118</v>
+        <v>689</v>
       </c>
       <c r="C3" t="n">
-        <v>4483</v>
+        <v>3375</v>
       </c>
       <c r="D3" t="n">
-        <v>17560</v>
+        <v>13427</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4306</v>
+        <v>1187</v>
       </c>
       <c r="C4" t="n">
-        <v>6897</v>
+        <v>5340</v>
       </c>
       <c r="D4" t="n">
-        <v>13192</v>
+        <v>11426</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2182</v>
+        <v>655</v>
       </c>
       <c r="C5" t="n">
-        <v>7189</v>
+        <v>8655</v>
       </c>
       <c r="D5" t="n">
-        <v>5103</v>
+        <v>5231</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1034</v>
+        <v>224</v>
       </c>
       <c r="C6" t="n">
-        <v>4625</v>
+        <v>6414</v>
       </c>
       <c r="D6" t="n">
-        <v>1366</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>179</v>
+        <v>66</v>
       </c>
       <c r="C7" t="n">
-        <v>2375</v>
+        <v>2220</v>
       </c>
       <c r="D7" t="n">
-        <v>583</v>
+        <v>604</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>971</v>
+        <v>722</v>
       </c>
       <c r="D8" t="n">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4100</v>
+        <v>469</v>
       </c>
       <c r="C2" t="n">
-        <v>1904</v>
+        <v>1250</v>
       </c>
       <c r="D2" t="n">
-        <v>12973</v>
+        <v>6464</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3887</v>
+        <v>681</v>
       </c>
       <c r="C3" t="n">
-        <v>3095</v>
+        <v>2408</v>
       </c>
       <c r="D3" t="n">
-        <v>15365</v>
+        <v>11678</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4092</v>
+        <v>802</v>
       </c>
       <c r="C4" t="n">
-        <v>5661</v>
+        <v>4081</v>
       </c>
       <c r="D4" t="n">
-        <v>13503</v>
+        <v>10956</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2691</v>
+        <v>621</v>
       </c>
       <c r="C5" t="n">
-        <v>6976</v>
+        <v>6305</v>
       </c>
       <c r="D5" t="n">
-        <v>6239</v>
+        <v>5517</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1342</v>
+        <v>224</v>
       </c>
       <c r="C6" t="n">
-        <v>5710</v>
+        <v>6109</v>
       </c>
       <c r="D6" t="n">
-        <v>1850</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>386</v>
+        <v>54</v>
       </c>
       <c r="C7" t="n">
-        <v>3324</v>
+        <v>2859</v>
       </c>
       <c r="D7" t="n">
-        <v>682</v>
+        <v>591</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>1498</v>
+        <v>831</v>
       </c>
       <c r="D8" t="n">
-        <v>399</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>508</v>
+        <v>271</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>127</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2923</v>
+        <v>574</v>
       </c>
       <c r="C2" t="n">
-        <v>2291</v>
+        <v>6521</v>
       </c>
       <c r="D2" t="n">
-        <v>10314</v>
+        <v>11465</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3465</v>
+        <v>487</v>
       </c>
       <c r="C3" t="n">
-        <v>2379</v>
+        <v>1550</v>
       </c>
       <c r="D3" t="n">
-        <v>14242</v>
+        <v>10115</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3711</v>
+        <v>648</v>
       </c>
       <c r="C4" t="n">
-        <v>4647</v>
+        <v>3064</v>
       </c>
       <c r="D4" t="n">
-        <v>13472</v>
+        <v>10649</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2965</v>
+        <v>640</v>
       </c>
       <c r="C5" t="n">
-        <v>6619</v>
+        <v>5038</v>
       </c>
       <c r="D5" t="n">
-        <v>7005</v>
+        <v>6341</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1579</v>
+        <v>367</v>
       </c>
       <c r="C6" t="n">
-        <v>6339</v>
+        <v>6141</v>
       </c>
       <c r="D6" t="n">
-        <v>2243</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>360</v>
+        <v>112</v>
       </c>
       <c r="C7" t="n">
-        <v>4135</v>
+        <v>4510</v>
       </c>
       <c r="D7" t="n">
-        <v>782</v>
+        <v>792</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>1935</v>
+        <v>1792</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>594</v>
+        <v>520</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>96</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4605</v>
+        <v>365</v>
       </c>
       <c r="C2" t="n">
-        <v>10257</v>
+        <v>8748</v>
       </c>
       <c r="D2" t="n">
-        <v>13565</v>
+        <v>12892</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2754</v>
+        <v>434</v>
       </c>
       <c r="C3" t="n">
-        <v>2080</v>
+        <v>3464</v>
       </c>
       <c r="D3" t="n">
-        <v>12859</v>
+        <v>9613</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3149</v>
+        <v>502</v>
       </c>
       <c r="C4" t="n">
-        <v>3570</v>
+        <v>2229</v>
       </c>
       <c r="D4" t="n">
-        <v>13173</v>
+        <v>10232</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2937</v>
+        <v>580</v>
       </c>
       <c r="C5" t="n">
-        <v>5667</v>
+        <v>3918</v>
       </c>
       <c r="D5" t="n">
-        <v>7593</v>
+        <v>6790</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1912</v>
+        <v>449</v>
       </c>
       <c r="C6" t="n">
-        <v>6394</v>
+        <v>5547</v>
       </c>
       <c r="D6" t="n">
-        <v>2853</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>669</v>
+        <v>197</v>
       </c>
       <c r="C7" t="n">
-        <v>5016</v>
+        <v>5275</v>
       </c>
       <c r="D7" t="n">
-        <v>960</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>134</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>2710</v>
+        <v>3016</v>
       </c>
       <c r="D8" t="n">
-        <v>450</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>1046</v>
+        <v>1068</v>
       </c>
       <c r="D9" t="n">
-        <v>305</v>
+        <v>225</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7575</v>
+        <v>3526</v>
       </c>
       <c r="C2" t="n">
-        <v>5184</v>
+        <v>12315</v>
       </c>
       <c r="D2" t="n">
-        <v>7225</v>
+        <v>10759</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3298</v>
+        <v>475</v>
       </c>
       <c r="C2" t="n">
-        <v>5826</v>
+        <v>10003</v>
       </c>
       <c r="D2" t="n">
-        <v>9983</v>
+        <v>11251</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3744</v>
+        <v>338</v>
       </c>
       <c r="C3" t="n">
-        <v>4156</v>
+        <v>5125</v>
       </c>
       <c r="D3" t="n">
-        <v>14098</v>
+        <v>9505</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4322</v>
+        <v>408</v>
       </c>
       <c r="C4" t="n">
-        <v>5387</v>
+        <v>2763</v>
       </c>
       <c r="D4" t="n">
-        <v>13510</v>
+        <v>9727</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1848</v>
+        <v>504</v>
       </c>
       <c r="C5" t="n">
-        <v>8649</v>
+        <v>3074</v>
       </c>
       <c r="D5" t="n">
-        <v>6937</v>
+        <v>7112</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>618</v>
+        <v>463</v>
       </c>
       <c r="C6" t="n">
-        <v>6231</v>
+        <v>4736</v>
       </c>
       <c r="D6" t="n">
-        <v>2216</v>
+        <v>3518</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>123</v>
+        <v>269</v>
       </c>
       <c r="C7" t="n">
-        <v>2655</v>
+        <v>5390</v>
       </c>
       <c r="D7" t="n">
-        <v>563</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>1025</v>
+        <v>3944</v>
       </c>
       <c r="D8" t="n">
-        <v>298</v>
+        <v>497</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>329</v>
+        <v>1820</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>154</v>
+        <v>608</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>91</v>
+        <v>201</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8382</v>
+        <v>3780</v>
       </c>
       <c r="C2" t="n">
-        <v>5364</v>
+        <v>8408</v>
       </c>
       <c r="D2" t="n">
-        <v>22709</v>
+        <v>24406</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3217</v>
+        <v>1166</v>
       </c>
       <c r="C3" t="n">
-        <v>2612</v>
+        <v>4863</v>
       </c>
       <c r="D3" t="n">
-        <v>1853</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5853</v>
+        <v>2203</v>
       </c>
       <c r="C2" t="n">
-        <v>6907</v>
+        <v>4076</v>
       </c>
       <c r="D2" t="n">
-        <v>23514</v>
+        <v>24793</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4762</v>
+        <v>2089</v>
       </c>
       <c r="C3" t="n">
-        <v>3595</v>
+        <v>6006</v>
       </c>
       <c r="D3" t="n">
-        <v>5220</v>
+        <v>5856</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1432</v>
+        <v>565</v>
       </c>
       <c r="C4" t="n">
-        <v>1574</v>
+        <v>3083</v>
       </c>
       <c r="D4" t="n">
-        <v>1554</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>853</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6194</v>
+        <v>1441</v>
       </c>
       <c r="C2" t="n">
-        <v>4897</v>
+        <v>5627</v>
       </c>
       <c r="D2" t="n">
-        <v>30211</v>
+        <v>27785</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4363</v>
+        <v>1770</v>
       </c>
       <c r="C3" t="n">
-        <v>4675</v>
+        <v>4212</v>
       </c>
       <c r="D3" t="n">
-        <v>7771</v>
+        <v>8606</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2634</v>
+        <v>1166</v>
       </c>
       <c r="C4" t="n">
-        <v>2685</v>
+        <v>4758</v>
       </c>
       <c r="D4" t="n">
-        <v>2210</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>635</v>
+        <v>288</v>
       </c>
       <c r="C5" t="n">
-        <v>955</v>
+        <v>1859</v>
       </c>
       <c r="D5" t="n">
-        <v>1215</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>262</v>
       </c>
       <c r="D6" t="n">
-        <v>903</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>115</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>629</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>286</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6355</v>
+        <v>1803</v>
       </c>
       <c r="C2" t="n">
-        <v>4815</v>
+        <v>11167</v>
       </c>
       <c r="D2" t="n">
-        <v>33299</v>
+        <v>27862</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4336</v>
+        <v>1333</v>
       </c>
       <c r="C3" t="n">
-        <v>4168</v>
+        <v>4313</v>
       </c>
       <c r="D3" t="n">
-        <v>10634</v>
+        <v>11055</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2944</v>
+        <v>1265</v>
       </c>
       <c r="C4" t="n">
-        <v>3698</v>
+        <v>4349</v>
       </c>
       <c r="D4" t="n">
-        <v>3157</v>
+        <v>3487</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1338</v>
+        <v>610</v>
       </c>
       <c r="C5" t="n">
-        <v>1831</v>
+        <v>3406</v>
       </c>
       <c r="D5" t="n">
-        <v>1338</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>337</v>
+        <v>180</v>
       </c>
       <c r="C6" t="n">
-        <v>622</v>
+        <v>1102</v>
       </c>
       <c r="D6" t="n">
-        <v>944</v>
+        <v>838</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>662</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>376</v>
+        <v>308</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>247</v>
       </c>
       <c r="D9" t="n">
-        <v>381</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7529</v>
+        <v>3601</v>
       </c>
       <c r="C2" t="n">
-        <v>9932</v>
+        <v>9366</v>
       </c>
       <c r="D2" t="n">
-        <v>29787</v>
+        <v>30684</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3867</v>
+        <v>1276</v>
       </c>
       <c r="C3" t="n">
-        <v>3685</v>
+        <v>6824</v>
       </c>
       <c r="D3" t="n">
-        <v>12541</v>
+        <v>12831</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2245</v>
+        <v>1115</v>
       </c>
       <c r="C4" t="n">
-        <v>3241</v>
+        <v>4239</v>
       </c>
       <c r="D4" t="n">
-        <v>3862</v>
+        <v>4761</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1124</v>
+        <v>806</v>
       </c>
       <c r="C5" t="n">
-        <v>2033</v>
+        <v>3824</v>
       </c>
       <c r="D5" t="n">
-        <v>1295</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>391</v>
+        <v>338</v>
       </c>
       <c r="C6" t="n">
-        <v>829</v>
+        <v>2240</v>
       </c>
       <c r="D6" t="n">
-        <v>769</v>
+        <v>903</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="C7" t="n">
-        <v>310</v>
+        <v>687</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>621</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
-        <v>271</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6904</v>
+        <v>2740</v>
       </c>
       <c r="C2" t="n">
-        <v>6908</v>
+        <v>7594</v>
       </c>
       <c r="D2" t="n">
-        <v>33470</v>
+        <v>37012</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4740</v>
+        <v>1887</v>
       </c>
       <c r="C3" t="n">
-        <v>6314</v>
+        <v>7040</v>
       </c>
       <c r="D3" t="n">
-        <v>14515</v>
+        <v>14519</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2683</v>
+        <v>1018</v>
       </c>
       <c r="C4" t="n">
-        <v>3442</v>
+        <v>5441</v>
       </c>
       <c r="D4" t="n">
-        <v>5457</v>
+        <v>6010</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1505</v>
+        <v>845</v>
       </c>
       <c r="C5" t="n">
-        <v>2698</v>
+        <v>3906</v>
       </c>
       <c r="D5" t="n">
-        <v>1773</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>696</v>
+        <v>488</v>
       </c>
       <c r="C6" t="n">
-        <v>1492</v>
+        <v>2962</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>225</v>
+        <v>195</v>
       </c>
       <c r="C7" t="n">
-        <v>604</v>
+        <v>1402</v>
       </c>
       <c r="D7" t="n">
-        <v>551</v>
+        <v>658</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>269</v>
+        <v>468</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>285</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>239</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>144</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6390</v>
+        <v>2513</v>
       </c>
       <c r="C2" t="n">
-        <v>3647</v>
+        <v>4738</v>
       </c>
       <c r="D2" t="n">
-        <v>30346</v>
+        <v>29296</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4765</v>
+        <v>2153</v>
       </c>
       <c r="C3" t="n">
-        <v>5745</v>
+        <v>9975</v>
       </c>
       <c r="D3" t="n">
-        <v>16502</v>
+        <v>15924</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3190</v>
+        <v>780</v>
       </c>
       <c r="C4" t="n">
-        <v>4997</v>
+        <v>7092</v>
       </c>
       <c r="D4" t="n">
-        <v>7030</v>
+        <v>5482</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1825</v>
+        <v>450</v>
       </c>
       <c r="C5" t="n">
-        <v>3048</v>
+        <v>2902</v>
       </c>
       <c r="D5" t="n">
-        <v>2374</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>999</v>
+        <v>180</v>
       </c>
       <c r="C6" t="n">
-        <v>2111</v>
+        <v>1373</v>
       </c>
       <c r="D6" t="n">
-        <v>1013</v>
+        <v>644</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>401</v>
+        <v>91</v>
       </c>
       <c r="C7" t="n">
-        <v>1059</v>
+        <v>458</v>
       </c>
       <c r="D7" t="n">
-        <v>599</v>
+        <v>446</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>439</v>
+        <v>279</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>144</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
